--- a/medical_surveys_questionnaires/022_sexual_health_wellness_check_in--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/022_sexual_health_wellness_check_in--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'gay'}</t>
+          <t>gay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Gay'}</t>
+          <t>Gay</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'lesbian'}</t>
+          <t>lesbian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Lesbian'}</t>
+          <t>Lesbian</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'bisexual'}</t>
+          <t>bisexual</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Bisexual'}</t>
+          <t>Bisexual</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'heterosexual'}</t>
+          <t>heterosexual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Heterosexual'}</t>
+          <t>Heterosexual</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'asexual'}</t>
+          <t>asexual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Asexual'}</t>
+          <t>Asexual</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'aromantic'}</t>
+          <t>aromantic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Aromantic'}</t>
+          <t>Aromantic</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'pansexual'}</t>
+          <t>pansexual</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Pansexual'}</t>
+          <t>Pansexual</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'polysex'}</t>
+          <t>polysex</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Polysex'}</t>
+          <t>Polysex</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer Not to Say'}</t>
+          <t>Prefer Not to Say</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'In a Relationship'}</t>
+          <t>In a Relationship</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_partnership'}</t>
+          <t>in_a_partnership</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'In a Partnership'}</t>
+          <t>In a Partnership</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer Not to Say'}</t>
+          <t>Prefer Not to Say</t>
         </is>
       </c>
     </row>
